--- a/inst/dados_premissas/2025/nomes_dist_powerbi.xlsx
+++ b/inst/dados_premissas/2025/nomes_dist_powerbi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Geracao Distribuida\PDE\PLAN26-30_1RQ\dados_premissas\2025_original\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Geracao Distribuida\PDE\PLAN26-30_2RQ\dados_premissas\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3F455C-59CF-432B-B70A-06D851C10AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B8E224-511E-4F18-A143-3462D1541245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="187">
   <si>
     <t>sig_agente</t>
   </si>
@@ -591,6 +591,12 @@
   </si>
   <si>
     <t>CPFL MOCOCA</t>
+  </si>
+  <si>
+    <t>Âmbar Amazonas</t>
+  </si>
+  <si>
+    <t>ÂMBAR ENERGIA RR</t>
   </si>
 </sst>
 </file>
@@ -997,14 +1003,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C178"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C180"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1028,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>180</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -1068,7 +1074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +1130,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
@@ -1132,7 +1138,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1164,7 +1170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>142</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>124</v>
       </c>
@@ -1228,7 +1234,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>143</v>
       </c>
@@ -1244,7 +1250,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>155</v>
       </c>
@@ -1252,7 +1258,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>135</v>
       </c>
@@ -1260,7 +1266,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -1268,7 +1274,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -1276,7 +1282,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -1284,7 +1290,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -1292,7 +1298,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1300,7 +1306,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1364,7 +1370,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -1372,7 +1378,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -1388,7 +1394,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>36</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -1404,7 +1410,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -1412,7 +1418,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -1428,7 +1434,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -1436,7 +1442,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>156</v>
       </c>
@@ -1444,7 +1450,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -1452,7 +1458,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>42</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -1468,7 +1474,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>45</v>
       </c>
@@ -1484,7 +1490,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>46</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>126</v>
       </c>
@@ -1508,7 +1514,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>47</v>
       </c>
@@ -1516,7 +1522,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>48</v>
       </c>
@@ -1524,7 +1530,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>49</v>
       </c>
@@ -1540,7 +1546,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>50</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>52</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>54</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>55</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>56</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>57</v>
       </c>
@@ -1612,7 +1618,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>58</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>125</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>59</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>60</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -1652,7 +1658,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>62</v>
       </c>
@@ -1660,7 +1666,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>63</v>
       </c>
@@ -1668,7 +1674,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>181</v>
       </c>
@@ -1676,7 +1682,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>140</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>67</v>
       </c>
@@ -1692,7 +1698,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>68</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -1708,7 +1714,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -1716,7 +1722,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>64</v>
       </c>
@@ -1724,7 +1730,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -1732,7 +1738,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>177</v>
       </c>
@@ -1740,7 +1746,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>157</v>
       </c>
@@ -1748,7 +1754,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>70</v>
       </c>
@@ -1756,7 +1762,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>65</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>137</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>71</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>72</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>73</v>
       </c>
@@ -1796,7 +1802,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>74</v>
       </c>
@@ -1804,7 +1810,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>75</v>
       </c>
@@ -1812,7 +1818,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>118</v>
       </c>
@@ -1820,7 +1826,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>134</v>
       </c>
@@ -1828,7 +1834,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>147</v>
       </c>
@@ -1836,7 +1842,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>76</v>
       </c>
@@ -1844,7 +1850,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>77</v>
       </c>
@@ -1852,7 +1858,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>148</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>78</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>79</v>
       </c>
@@ -1876,7 +1882,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>80</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>81</v>
       </c>
@@ -1892,7 +1898,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -1900,7 +1906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>83</v>
       </c>
@@ -1908,7 +1914,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>84</v>
       </c>
@@ -1916,7 +1922,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>149</v>
       </c>
@@ -1924,7 +1930,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>131</v>
       </c>
@@ -1932,7 +1938,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>85</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>86</v>
       </c>
@@ -1948,7 +1954,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>87</v>
       </c>
@@ -1956,7 +1962,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>158</v>
       </c>
@@ -1964,7 +1970,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>88</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -1980,7 +1986,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>159</v>
       </c>
@@ -1988,7 +1994,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>160</v>
       </c>
@@ -1996,7 +2002,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>161</v>
       </c>
@@ -2004,7 +2010,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>162</v>
       </c>
@@ -2012,7 +2018,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -2021,7 +2027,7 @@
       </c>
       <c r="C127" s="2"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>164</v>
       </c>
@@ -2029,7 +2035,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>165</v>
       </c>
@@ -2037,7 +2043,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>166</v>
       </c>
@@ -2045,7 +2051,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>167</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>168</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>169</v>
       </c>
@@ -2069,7 +2075,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2077,7 +2083,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>89</v>
       </c>
@@ -2085,7 +2091,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>31</v>
       </c>
@@ -2093,7 +2099,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>182</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -2109,7 +2115,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>183</v>
       </c>
@@ -2117,7 +2123,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>90</v>
       </c>
@@ -2125,7 +2131,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>113</v>
       </c>
@@ -2133,7 +2139,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -2141,7 +2147,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>94</v>
       </c>
@@ -2149,7 +2155,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>95</v>
       </c>
@@ -2157,7 +2163,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>96</v>
       </c>
@@ -2165,7 +2171,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>97</v>
       </c>
@@ -2173,7 +2179,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -2181,7 +2187,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>98</v>
       </c>
@@ -2189,7 +2195,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>132</v>
       </c>
@@ -2197,7 +2203,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>99</v>
       </c>
@@ -2205,7 +2211,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -2213,7 +2219,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>139</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>170</v>
       </c>
@@ -2229,7 +2235,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>171</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>172</v>
       </c>
@@ -2245,7 +2251,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>138</v>
       </c>
@@ -2253,7 +2259,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>173</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>174</v>
       </c>
@@ -2269,7 +2275,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>130</v>
       </c>
@@ -2277,7 +2283,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>100</v>
       </c>
@@ -2285,7 +2291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>178</v>
       </c>
@@ -2293,7 +2299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>175</v>
       </c>
@@ -2301,7 +2307,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>101</v>
       </c>
@@ -2309,7 +2315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>176</v>
       </c>
@@ -2317,7 +2323,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>102</v>
       </c>
@@ -2325,7 +2331,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>103</v>
       </c>
@@ -2333,12 +2339,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>105</v>
       </c>
@@ -2346,7 +2352,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>128</v>
       </c>
@@ -2354,7 +2360,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>129</v>
       </c>
@@ -2362,7 +2368,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>121</v>
       </c>
@@ -2370,7 +2376,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>120</v>
       </c>
@@ -2378,7 +2384,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>91</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>110</v>
       </c>
@@ -2394,7 +2400,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>92</v>
       </c>
@@ -2402,7 +2408,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>112</v>
       </c>
@@ -2410,7 +2416,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>184</v>
       </c>
@@ -2418,21 +2424,40 @@
         <v>114</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B178" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>185</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B167" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A2:A176">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A136:A167">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A179:A180">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
